--- a/tests/fixtures/18_billing_statement/18_billing_statement_pattern-from-draft.xlsx
+++ b/tests/fixtures/18_billing_statement/18_billing_statement_pattern-from-draft.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -464,54 +464,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>col_date</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -521,7 +511,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>col_type</t>
+          <t>col_date</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -531,7 +521,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -548,7 +538,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>col_invoice</t>
+          <t>col_type</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -558,7 +548,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Invoice #</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -575,7 +565,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>col_description</t>
+          <t>col_invoice</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -585,7 +575,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Invoice #</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -602,7 +592,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>col_amount</t>
+          <t>col_description</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -612,7 +602,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -629,7 +619,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>col_payment</t>
+          <t>col_amount</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -639,7 +629,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -656,7 +646,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>col_balance</t>
+          <t>col_payment</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -666,7 +656,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -676,31 +666,31 @@
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>stmt.number</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>col_balance</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -710,12 +700,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>stmt.date</t>
+          <t>stmt.number</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -737,12 +727,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>stmt.customer_id</t>
+          <t>stmt.date</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -764,7 +754,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>stmt.bill_to_name</t>
+          <t>stmt.customer_id</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -791,15 +781,19 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>line.date</t>
+          <t>stmt.bill_to_name</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -814,19 +808,15 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>line.type</t>
+          <t>line.date</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -841,17 +831,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>line.invoice</t>
+          <t>line.type</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
@@ -868,17 +858,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>line.description</t>
+          <t>line.invoice</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
@@ -895,12 +885,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>line.amount</t>
+          <t>line.description</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -922,7 +912,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>line.payment</t>
+          <t>line.amount</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -949,7 +939,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>line.balance</t>
+          <t>line.payment</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -976,7 +966,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>remittance.amount_due</t>
+          <t>line.balance</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -996,48 +986,56 @@
       <c r="I20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>remittance.amount_due</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>cell:C8</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>stmt.number</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>cell:F8</t>
+          <t>cell:C8</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>stmt.bill_to_name</t>
+          <t>stmt.number</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -1051,12 +1049,12 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>cell:C9</t>
+          <t>cell:F8</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>stmt.date</t>
+          <t>stmt.bill_to_name</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -1070,12 +1068,12 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>cell:C10</t>
+          <t>cell:C9</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>stmt.customer_id</t>
+          <t>stmt.date</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
@@ -1087,139 +1085,158 @@
       <c r="I25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>cell:C10</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>stmt.customer_id</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>col_date</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>col_type</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>col_invoice</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>col_description</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>col_amount</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>col_payment</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>col_balance</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>line.date</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>line.type</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>line.invoice</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>line.description</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>line.amount</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>line.payment</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>line.balance</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>cell:C30</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>remittance.amount_due</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
